--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>603</v>
+        <v>788</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>430</v>
+        <v>574</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>03288</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TOMBOLO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03288</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>TOMBOLO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="J17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
@@ -1211,23 +1211,23 @@
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="J20" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>185</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.01081081081081081</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>187</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.2513368983957219</v>
+        <v>47</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>117</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.5897435897435898</v>
+        <v>69</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>173</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.02890173410404624</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>137</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.0218978102189781</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>68</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1911764705882353</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>81</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>3</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>94</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.2978723404255319</v>
+        <v>28</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.375</v>
+        <v>18</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>788</v>
+        <v>844</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03317</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>TOMBOLO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -821,42 +821,42 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03288</t>
+          <t>03317</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>03288</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TOMBOLO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>4</v>
@@ -995,16 +995,16 @@
         <v>6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>5</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>9</v>
@@ -1049,16 +1049,16 @@
         <v>2</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>12</v>
@@ -1112,10 +1112,10 @@
         <v>19</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>34</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13</v>
@@ -1180,7 +1180,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>03276</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1199,42 +1199,42 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03276</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>16</v>
@@ -1325,13 +1325,13 @@
         <v>9</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>844</v>
+        <v>882</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>4</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>8</v>
@@ -941,19 +941,19 @@
         <v>13</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>4</v>
@@ -995,16 +995,16 @@
         <v>6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>5</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>34</v>
@@ -1109,13 +1109,13 @@
         <v>12</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>80</v>
@@ -1265,16 +1265,16 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>3</v>
@@ -1310,13 +1310,13 @@
         <v>37</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>16</v>
@@ -1328,14 +1328,14 @@
         <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>882</v>
+        <v>927</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>626</v>
+        <v>661</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>21</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>78</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>52</v>
@@ -950,14 +950,14 @@
         <v>9</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>5</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>10</v>
@@ -1049,16 +1049,16 @@
         <v>3</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>5</v>
@@ -1166,7 +1166,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>17</v>
@@ -1211,16 +1211,16 @@
         <v>14</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>29</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         <v>10</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>3</v>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>9</v>
@@ -1328,10 +1328,10 @@
         <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N20" headerRowCount="1">
-  <autoFilter ref="A10:N20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N21" headerRowCount="1">
+  <autoFilter ref="A10:N21"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>927</v>
+        <v>971</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>5</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>5</v>
@@ -1166,7 +1166,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>29</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         <v>10</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>3</v>
@@ -1307,35 +1307,89 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>53921</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>PADOVA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>BETTIOLO ROBERTO</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N21" headerRowCount="1">
-  <autoFilter ref="A10:N21"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O21" headerRowCount="1">
+  <autoFilter ref="A10:O21"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA SOMMAVILLA 109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA ARMISTIZIO 180</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>157</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA GATTAMELATA 24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>LOC. PONTE DI BRENTA SNC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>ROMA 270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>164</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>ALESSIO VALERIO 54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>CORSO STATI UNITI 27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA VICENZA</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>40</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>C.SO 1 MAGGIO</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>ROMEA 21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>TRE PONTI 13/C</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>BETTIOLO ROBERTO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>971</v>
+        <v>1010</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>55</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,52 +960,52 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03211</t>
+          <t>03244</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>ALBIGNASEGO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LOC. PONTE DI BRENTA SNC</t>
+          <t>ROMA 270</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>5</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03244</t>
+          <t>03211</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ALBIGNASEGO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ROMA 270</t>
+          <t>LOC. PONTE DI BRENTA SNC</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>153</v>
+        <v>235</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>11</v>
@@ -1149,19 +1149,19 @@
         <v>20</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
         <v>25</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>17</v>
@@ -1273,13 +1273,13 @@
         <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>22</v>
@@ -1391,10 +1391,10 @@
         <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>22</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>716</v>
+        <v>756</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,17 +818,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>03317</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TOMBOLO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIA SOMMAVILLA 109</t>
+          <t>VIA ARMISTIZIO 180</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -842,52 +842,52 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H11" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="J11" s="12" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>144</v>
+        <v>258</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03317</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>TOMBOLO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA ARMISTIZIO 180</t>
+          <t>VIA SOMMAVILLA 109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>13</v>
@@ -1037,10 +1037,10 @@
         <v>40</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>5</v>
@@ -1081,28 +1081,28 @@
         <v>121</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>17</v>
@@ -1267,7 +1267,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>15</v>
@@ -1276,7 +1276,7 @@
         <v>18</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>30</v>
@@ -1317,7 +1317,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>22</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1060</v>
+        <v>1126</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>756</v>
+        <v>793</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,17 +818,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03317</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>TOMBOLO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIA ARMISTIZIO 180</t>
+          <t>VIA SOMMAVILLA 109</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -842,52 +842,52 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>03317</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TOMBOLO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA SOMMAVILLA 109</t>
+          <t>VIA ARMISTIZIO 180</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
@@ -1090,19 +1090,19 @@
         <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>17</v>
@@ -1267,23 +1267,23 @@
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1376,13 +1376,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>36</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>24</v>
@@ -1394,7 +1394,7 @@
         <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>22</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>793</v>
+        <v>827</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>20</v>
@@ -972,23 +972,23 @@
         <v>14</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>5</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>8</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         <v>67</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>40</v>
@@ -1217,7 +1217,7 @@
         <v>29</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1376,13 +1376,13 @@
         <v>47</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>24</v>
@@ -1394,10 +1394,10 @@
         <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1173</v>
+        <v>1233</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>827</v>
+        <v>870</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>11</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>18</v>
@@ -1158,10 +1158,10 @@
         <v>38</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>16</v>
@@ -1276,10 +1276,10 @@
         <v>20</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>1</v>
@@ -1332,10 +1332,10 @@
         <v>11</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>52</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1453,14 +1453,14 @@
         <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1233</v>
+        <v>1293</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>870</v>
+        <v>919</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>7</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>9</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H17" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="K17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>19</v>
@@ -1267,19 +1267,19 @@
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>55</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>32</v>
@@ -1335,7 +1335,7 @@
         <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>3</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>52</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>27</v>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1293</v>
+        <v>1338</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>919</v>
+        <v>948</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>42</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>98</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>12</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>19</v>
@@ -1273,13 +1273,13 @@
         <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>55471</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>LEGNARO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>C.SO 1 MAGGIO</t>
+          <t>ROMEA 21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LEGNARO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ROMEA 21</t>
+          <t>C.SO 1 MAGGIO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1453,14 +1453,14 @@
         <v>0</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR BETTIOLO ROBERTO.xlsx
@@ -684,13 +684,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,17 +818,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>03317</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TOMBOLO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIA SOMMAVILLA 109</t>
+          <t>VIA ARMISTIZIO 180</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03317</t>
+          <t>03288</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA ARMISTIZIO 180</t>
+          <t>VIA GATTAMELATA 24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -901,52 +901,52 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03288</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>TOMBOLO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA GATTAMELATA 24</t>
+          <t>VIA SOMMAVILLA 109</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>341</v>
+        <v>199</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>209</v>
@@ -1031,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>49</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>9</v>
@@ -1090,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>33</v>
@@ -1099,7 +1099,7 @@
         <v>58</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>10</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>30</v>
@@ -1149,7 +1149,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>132</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>12</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>19</v>
@@ -1267,7 +1267,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>16</v>
@@ -1276,7 +1276,7 @@
         <v>23</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>35</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LEGNARO</t>
+          <t>PADOVA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ROMEA 21</t>
+          <t>C.SO 1 MAGGIO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1317,28 +1317,28 @@
         <v>56</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>55471</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PADOVA</t>
+          <t>LEGNARO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>C.SO 1 MAGGIO</t>
+          <t>ROMEA 21</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1376,28 +1376,28 @@
         <v>56</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>7</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
